--- a/data/satisfaction_summary/2026/6月/6月客户类型满意度汇总表.xlsx
+++ b/data/satisfaction_summary/2026/6月/6月客户类型满意度汇总表.xlsx
@@ -586,20 +586,22 @@
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>9.91</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>9.74</v>
+        <v>9.59</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" s="4" t="n"/>
+        <v>9.92</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>9</v>
+      </c>
       <c r="H3" s="4" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1">
@@ -610,20 +612,20 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9.42</v>
+        <v>9.52</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>9.94</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>9.15</v>
+        <v>9.16</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>9.17</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1">
@@ -634,7 +636,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>9.75</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>10</v>
@@ -643,11 +645,11 @@
         <v>9.460000000000001</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.69</v>
       </c>
       <c r="G5" s="4" t="n"/>
       <c r="H5" s="4" t="n">
-        <v>9.17</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1">
@@ -682,20 +684,20 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10</v>
+        <v>9.94</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.789999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9.83</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G7" s="4" t="n"/>
       <c r="H7" s="4" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1">
@@ -706,20 +708,20 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.83</v>
+        <v>9.84</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9.859999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G8" s="4" t="n"/>
       <c r="H8" s="4" t="n">
-        <v>9.56</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1">
@@ -734,7 +736,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.77</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
@@ -742,7 +744,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.56</v>
+        <v>9.59</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -751,7 +753,7 @@
       </c>
       <c r="G9" s="4" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1">
@@ -762,7 +764,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.33</v>
+        <v>9.51</v>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
@@ -770,7 +772,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
@@ -779,7 +781,7 @@
       </c>
       <c r="G10" s="4" t="n"/>
       <c r="H10" s="4" t="n">
-        <v>9.449999999999999</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1">
@@ -818,7 +820,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>10</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
@@ -835,7 +837,7 @@
       </c>
       <c r="G12" s="4" t="n"/>
       <c r="H12" s="4" t="n">
-        <v>10</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1">
@@ -898,10 +900,10 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>9.75</v>
@@ -996,13 +998,13 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>10</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="D17" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
@@ -1010,7 +1012,9 @@
         </is>
       </c>
       <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="H17" s="4" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="18" ht="24" customHeight="1">
       <c r="A18" s="5" t="n"/>
@@ -1020,13 +1024,13 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>9.98</v>
+        <v>9.93</v>
       </c>
       <c r="D18" s="4" t="n">
         <v>10</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>9.949999999999999</v>
+        <v>9.82</v>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
@@ -1106,7 +1110,7 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
@@ -1126,22 +1130,22 @@
       </c>
       <c r="B22" s="2" t="n"/>
       <c r="C22" s="4" t="n">
-        <v>9.779999999999999</v>
+        <v>9.74</v>
       </c>
       <c r="D22" s="4" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9.66</v>
+        <v>9.68</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>9.359999999999999</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
   </sheetData>
